--- a/tests/agent_contract/data/H3_sales_multi_amount.xlsx
+++ b/tests/agent_contract/data/H3_sales_multi_amount.xlsx
@@ -461,24 +461,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2420.9</v>
+        <v>3438.64</v>
       </c>
       <c r="D2" t="n">
-        <v>2735.62</v>
+        <v>3885.66</v>
       </c>
       <c r="E2" t="n">
-        <v>2420.9</v>
+        <v>3438.64</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
@@ -490,24 +490,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4088.91</v>
+        <v>4753.27</v>
       </c>
       <c r="D3" t="n">
-        <v>4620.47</v>
+        <v>5371.2</v>
       </c>
       <c r="E3" t="n">
-        <v>3658.17</v>
+        <v>4753.27</v>
       </c>
       <c r="F3" t="n">
-        <v>430.74</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
@@ -519,24 +519,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4209.46</v>
+        <v>287.65</v>
       </c>
       <c r="D4" t="n">
-        <v>4756.69</v>
+        <v>325.04</v>
       </c>
       <c r="E4" t="n">
-        <v>4209.46</v>
+        <v>287.65</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -548,24 +548,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2537.28</v>
+        <v>2146.49</v>
       </c>
       <c r="D5" t="n">
-        <v>2867.13</v>
+        <v>2425.53</v>
       </c>
       <c r="E5" t="n">
-        <v>2537.28</v>
+        <v>2146.49</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
     </row>
@@ -577,24 +577,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3148.61</v>
+        <v>1310.03</v>
       </c>
       <c r="D6" t="n">
-        <v>3557.93</v>
+        <v>1480.33</v>
       </c>
       <c r="E6" t="n">
-        <v>3148.61</v>
+        <v>1310.03</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
@@ -610,20 +610,20 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3823.19</v>
+        <v>2497.87</v>
       </c>
       <c r="D7" t="n">
-        <v>4320.2</v>
+        <v>2822.59</v>
       </c>
       <c r="E7" t="n">
-        <v>3823.19</v>
+        <v>2497.87</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -635,24 +635,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3921.46</v>
+        <v>1840.04</v>
       </c>
       <c r="D8" t="n">
-        <v>4431.25</v>
+        <v>2079.25</v>
       </c>
       <c r="E8" t="n">
-        <v>3921.46</v>
+        <v>1560.32</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>279.72</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -664,24 +664,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1776.57</v>
+        <v>1034.2</v>
       </c>
       <c r="D9" t="n">
-        <v>2007.52</v>
+        <v>1168.65</v>
       </c>
       <c r="E9" t="n">
-        <v>1776.57</v>
+        <v>1034.2</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -693,24 +693,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>399.85</v>
+        <v>1082.95</v>
       </c>
       <c r="D10" t="n">
-        <v>451.83</v>
+        <v>1223.73</v>
       </c>
       <c r="E10" t="n">
-        <v>399.85</v>
+        <v>1082.95</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -722,24 +722,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4735.71</v>
+        <v>1489.14</v>
       </c>
       <c r="D11" t="n">
-        <v>5351.35</v>
+        <v>1682.73</v>
       </c>
       <c r="E11" t="n">
-        <v>4735.71</v>
+        <v>1489.14</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
@@ -755,20 +755,20 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2624.08</v>
+        <v>1513.3</v>
       </c>
       <c r="D12" t="n">
-        <v>2965.21</v>
+        <v>1710.03</v>
       </c>
       <c r="E12" t="n">
-        <v>2624.08</v>
+        <v>1513.3</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -780,24 +780,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2908.21</v>
+        <v>1091.11</v>
       </c>
       <c r="D13" t="n">
-        <v>3286.28</v>
+        <v>1232.95</v>
       </c>
       <c r="E13" t="n">
-        <v>2908.21</v>
+        <v>1091.11</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
     </row>
@@ -809,24 +809,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2096.89</v>
+        <v>2469.15</v>
       </c>
       <c r="D14" t="n">
-        <v>2369.49</v>
+        <v>2790.14</v>
       </c>
       <c r="E14" t="n">
-        <v>2096.89</v>
+        <v>2469.15</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
@@ -838,24 +838,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3136.07</v>
+        <v>1578.25</v>
       </c>
       <c r="D15" t="n">
-        <v>3543.76</v>
+        <v>1783.42</v>
       </c>
       <c r="E15" t="n">
-        <v>3136.07</v>
+        <v>1424.86</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>153.39</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -867,24 +867,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>912.8200000000001</v>
+        <v>3512.21</v>
       </c>
       <c r="D16" t="n">
-        <v>1031.49</v>
+        <v>3968.8</v>
       </c>
       <c r="E16" t="n">
-        <v>912.8200000000001</v>
+        <v>3512.21</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -896,24 +896,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1591.27</v>
+        <v>1901.77</v>
       </c>
       <c r="D17" t="n">
-        <v>1798.14</v>
+        <v>2149</v>
       </c>
       <c r="E17" t="n">
-        <v>1591.27</v>
+        <v>1901.77</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -925,24 +925,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4273.48</v>
+        <v>4087.54</v>
       </c>
       <c r="D18" t="n">
-        <v>4829.03</v>
+        <v>4618.92</v>
       </c>
       <c r="E18" t="n">
-        <v>3583.02</v>
+        <v>4087.54</v>
       </c>
       <c r="F18" t="n">
-        <v>690.46</v>
+        <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
@@ -954,24 +954,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2551.61</v>
+        <v>1879.43</v>
       </c>
       <c r="D19" t="n">
-        <v>2883.32</v>
+        <v>2123.76</v>
       </c>
       <c r="E19" t="n">
-        <v>2551.61</v>
+        <v>1879.43</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -983,24 +983,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>484.45</v>
+        <v>4383.34</v>
       </c>
       <c r="D20" t="n">
-        <v>547.4299999999999</v>
+        <v>4953.17</v>
       </c>
       <c r="E20" t="n">
-        <v>484.45</v>
+        <v>4383.34</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
@@ -1012,24 +1012,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4905.69</v>
+        <v>458.79</v>
       </c>
       <c r="D21" t="n">
-        <v>5543.43</v>
+        <v>518.4299999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>3952.78</v>
+        <v>458.79</v>
       </c>
       <c r="F21" t="n">
-        <v>952.91</v>
+        <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -1045,20 +1045,20 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4317.06</v>
+        <v>2379.06</v>
       </c>
       <c r="D22" t="n">
-        <v>4878.28</v>
+        <v>2688.34</v>
       </c>
       <c r="E22" t="n">
-        <v>4317.06</v>
+        <v>2379.06</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -1074,20 +1074,20 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4187.44</v>
+        <v>3969.98</v>
       </c>
       <c r="D23" t="n">
-        <v>4731.81</v>
+        <v>4486.08</v>
       </c>
       <c r="E23" t="n">
-        <v>4187.44</v>
+        <v>3969.98</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -1099,24 +1099,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3526.79</v>
+        <v>377.06</v>
       </c>
       <c r="D24" t="n">
-        <v>3985.27</v>
+        <v>426.08</v>
       </c>
       <c r="E24" t="n">
-        <v>3526.79</v>
+        <v>377.06</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -1128,24 +1128,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1911.44</v>
+        <v>825.09</v>
       </c>
       <c r="D25" t="n">
-        <v>2159.93</v>
+        <v>932.35</v>
       </c>
       <c r="E25" t="n">
-        <v>1911.44</v>
+        <v>825.09</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-07-12</t>
         </is>
       </c>
     </row>
@@ -1157,24 +1157,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>296.66</v>
+        <v>3287.17</v>
       </c>
       <c r="D26" t="n">
-        <v>335.23</v>
+        <v>3714.5</v>
       </c>
       <c r="E26" t="n">
-        <v>296.66</v>
+        <v>3287.17</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -1190,20 +1190,20 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3091.39</v>
+        <v>3398.15</v>
       </c>
       <c r="D27" t="n">
-        <v>3493.27</v>
+        <v>3839.91</v>
       </c>
       <c r="E27" t="n">
-        <v>3091.39</v>
+        <v>3398.15</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
@@ -1215,24 +1215,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3940.53</v>
+        <v>2310.34</v>
       </c>
       <c r="D28" t="n">
-        <v>4452.8</v>
+        <v>2610.68</v>
       </c>
       <c r="E28" t="n">
-        <v>3940.53</v>
+        <v>2310.34</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
@@ -1248,20 +1248,20 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2993.86</v>
+        <v>4020.31</v>
       </c>
       <c r="D29" t="n">
-        <v>3383.06</v>
+        <v>4542.95</v>
       </c>
       <c r="E29" t="n">
-        <v>2993.86</v>
+        <v>3248.52</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>771.79</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -1277,20 +1277,20 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2292.08</v>
+        <v>1469.22</v>
       </c>
       <c r="D30" t="n">
-        <v>2590.05</v>
+        <v>1660.22</v>
       </c>
       <c r="E30" t="n">
-        <v>2292.08</v>
+        <v>1469.22</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -1302,24 +1302,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3571.5</v>
+        <v>2069.49</v>
       </c>
       <c r="D31" t="n">
-        <v>4035.79</v>
+        <v>2338.52</v>
       </c>
       <c r="E31" t="n">
-        <v>3140.06</v>
+        <v>2069.49</v>
       </c>
       <c r="F31" t="n">
-        <v>431.44</v>
+        <v>0</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -1331,24 +1331,24 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4583.44</v>
+        <v>2686.4</v>
       </c>
       <c r="D32" t="n">
-        <v>5179.29</v>
+        <v>3035.63</v>
       </c>
       <c r="E32" t="n">
-        <v>3774.85</v>
+        <v>2686.4</v>
       </c>
       <c r="F32" t="n">
-        <v>808.59</v>
+        <v>0</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
     </row>
@@ -1364,20 +1364,20 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4301.95</v>
+        <v>4656.07</v>
       </c>
       <c r="D33" t="n">
-        <v>4861.2</v>
+        <v>5261.36</v>
       </c>
       <c r="E33" t="n">
-        <v>4301.95</v>
+        <v>4656.07</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -1389,24 +1389,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4158.68</v>
+        <v>703.73</v>
       </c>
       <c r="D34" t="n">
-        <v>4699.31</v>
+        <v>795.21</v>
       </c>
       <c r="E34" t="n">
-        <v>3975.55</v>
+        <v>703.73</v>
       </c>
       <c r="F34" t="n">
-        <v>183.13</v>
+        <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -1422,20 +1422,20 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>298.69</v>
+        <v>4054.52</v>
       </c>
       <c r="D35" t="n">
-        <v>337.52</v>
+        <v>4581.61</v>
       </c>
       <c r="E35" t="n">
-        <v>246.8</v>
+        <v>4054.52</v>
       </c>
       <c r="F35" t="n">
-        <v>51.89</v>
+        <v>0</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-14</t>
         </is>
       </c>
     </row>
@@ -1447,24 +1447,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>880.29</v>
+        <v>4508.92</v>
       </c>
       <c r="D36" t="n">
-        <v>994.73</v>
+        <v>5095.08</v>
       </c>
       <c r="E36" t="n">
-        <v>880.29</v>
+        <v>4508.92</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
@@ -1476,24 +1476,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4744.21</v>
+        <v>2258.03</v>
       </c>
       <c r="D37" t="n">
-        <v>5360.96</v>
+        <v>2551.57</v>
       </c>
       <c r="E37" t="n">
-        <v>4744.21</v>
+        <v>2258.03</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
@@ -1505,24 +1505,24 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4943.4</v>
+        <v>4825.89</v>
       </c>
       <c r="D38" t="n">
-        <v>5586.04</v>
+        <v>5453.26</v>
       </c>
       <c r="E38" t="n">
-        <v>4943.4</v>
+        <v>4825.89</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -1534,24 +1534,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3203.8</v>
+        <v>171.68</v>
       </c>
       <c r="D39" t="n">
-        <v>3620.29</v>
+        <v>194</v>
       </c>
       <c r="E39" t="n">
-        <v>3203.8</v>
+        <v>171.68</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -1563,24 +1563,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1749.73</v>
+        <v>1806.08</v>
       </c>
       <c r="D40" t="n">
-        <v>1977.19</v>
+        <v>2040.87</v>
       </c>
       <c r="E40" t="n">
-        <v>1749.73</v>
+        <v>1806.08</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
@@ -1592,24 +1592,24 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4142.2</v>
+        <v>3201.74</v>
       </c>
       <c r="D41" t="n">
-        <v>4680.69</v>
+        <v>3617.97</v>
       </c>
       <c r="E41" t="n">
-        <v>4056.16</v>
+        <v>3201.74</v>
       </c>
       <c r="F41" t="n">
-        <v>86.04000000000001</v>
+        <v>0</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
@@ -1625,20 +1625,20 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1537.44</v>
+        <v>4477.31</v>
       </c>
       <c r="D42" t="n">
-        <v>1737.31</v>
+        <v>5059.36</v>
       </c>
       <c r="E42" t="n">
-        <v>1537.44</v>
+        <v>3758.14</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>719.17</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1650,24 +1650,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>696.37</v>
+        <v>3070.84</v>
       </c>
       <c r="D43" t="n">
-        <v>786.9</v>
+        <v>3470.05</v>
       </c>
       <c r="E43" t="n">
-        <v>601.73</v>
+        <v>3070.84</v>
       </c>
       <c r="F43" t="n">
-        <v>94.64</v>
+        <v>0</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -1679,24 +1679,24 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>280.69</v>
+        <v>2172.55</v>
       </c>
       <c r="D44" t="n">
-        <v>317.18</v>
+        <v>2454.98</v>
       </c>
       <c r="E44" t="n">
-        <v>280.69</v>
+        <v>2143.17</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>29.38</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -1708,24 +1708,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4394.39</v>
+        <v>3365.51</v>
       </c>
       <c r="D45" t="n">
-        <v>4965.66</v>
+        <v>3803.03</v>
       </c>
       <c r="E45" t="n">
-        <v>4394.39</v>
+        <v>3365.51</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -1737,24 +1737,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>340.79</v>
+        <v>244.14</v>
       </c>
       <c r="D46" t="n">
-        <v>385.09</v>
+        <v>275.88</v>
       </c>
       <c r="E46" t="n">
-        <v>340.79</v>
+        <v>244.14</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
@@ -1766,24 +1766,24 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>779.64</v>
+        <v>4656.67</v>
       </c>
       <c r="D47" t="n">
-        <v>880.99</v>
+        <v>5262.04</v>
       </c>
       <c r="E47" t="n">
-        <v>779.64</v>
+        <v>4656.67</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -1799,20 +1799,20 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3912.1</v>
+        <v>4476.94</v>
       </c>
       <c r="D48" t="n">
-        <v>4420.67</v>
+        <v>5058.94</v>
       </c>
       <c r="E48" t="n">
-        <v>3912.1</v>
+        <v>4476.94</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -1824,24 +1824,24 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1787.63</v>
+        <v>2743.43</v>
       </c>
       <c r="D49" t="n">
-        <v>2020.02</v>
+        <v>3100.08</v>
       </c>
       <c r="E49" t="n">
-        <v>1787.63</v>
+        <v>2743.43</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -1853,24 +1853,24 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3274.03</v>
+        <v>2962.3</v>
       </c>
       <c r="D50" t="n">
-        <v>3699.65</v>
+        <v>3347.4</v>
       </c>
       <c r="E50" t="n">
-        <v>3274.03</v>
+        <v>2962.3</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
@@ -1882,24 +1882,24 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1117.38</v>
+        <v>3436.5</v>
       </c>
       <c r="D51" t="n">
-        <v>1262.64</v>
+        <v>3883.24</v>
       </c>
       <c r="E51" t="n">
-        <v>1004.16</v>
+        <v>3436.5</v>
       </c>
       <c r="F51" t="n">
-        <v>113.22</v>
+        <v>0</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -1915,20 +1915,20 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3733.74</v>
+        <v>1635.28</v>
       </c>
       <c r="D52" t="n">
-        <v>4219.13</v>
+        <v>1847.87</v>
       </c>
       <c r="E52" t="n">
-        <v>3733.74</v>
+        <v>1635.28</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
@@ -1940,24 +1940,24 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>208.61</v>
+        <v>1204.06</v>
       </c>
       <c r="D53" t="n">
-        <v>235.73</v>
+        <v>1360.59</v>
       </c>
       <c r="E53" t="n">
-        <v>208.61</v>
+        <v>1204.06</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -1969,24 +1969,24 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2289.46</v>
+        <v>1575.6</v>
       </c>
       <c r="D54" t="n">
-        <v>2587.09</v>
+        <v>1780.43</v>
       </c>
       <c r="E54" t="n">
-        <v>2289.46</v>
+        <v>1575.6</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -1998,24 +1998,24 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>537.54</v>
+        <v>850.9299999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>607.42</v>
+        <v>961.55</v>
       </c>
       <c r="E55" t="n">
-        <v>537.54</v>
+        <v>850.9299999999999</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -2027,24 +2027,24 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3822.32</v>
+        <v>2189</v>
       </c>
       <c r="D56" t="n">
-        <v>4319.22</v>
+        <v>2473.57</v>
       </c>
       <c r="E56" t="n">
-        <v>3822.32</v>
+        <v>2189</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -2060,20 +2060,20 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>934.15</v>
+        <v>4624.59</v>
       </c>
       <c r="D57" t="n">
-        <v>1055.59</v>
+        <v>5225.79</v>
       </c>
       <c r="E57" t="n">
-        <v>934.15</v>
+        <v>4624.59</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -2085,24 +2085,24 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>758.33</v>
+        <v>2070.17</v>
       </c>
       <c r="D58" t="n">
-        <v>856.91</v>
+        <v>2339.29</v>
       </c>
       <c r="E58" t="n">
-        <v>758.33</v>
+        <v>2070.17</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -2114,24 +2114,24 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3360.23</v>
+        <v>4198.74</v>
       </c>
       <c r="D59" t="n">
-        <v>3797.06</v>
+        <v>4744.58</v>
       </c>
       <c r="E59" t="n">
-        <v>3360.23</v>
+        <v>4198.74</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -2143,24 +2143,24 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4104.35</v>
+        <v>379.24</v>
       </c>
       <c r="D60" t="n">
-        <v>4637.92</v>
+        <v>428.54</v>
       </c>
       <c r="E60" t="n">
-        <v>3817.59</v>
+        <v>379.24</v>
       </c>
       <c r="F60" t="n">
-        <v>286.76</v>
+        <v>0</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
@@ -2172,24 +2172,24 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1804.18</v>
+        <v>1559.01</v>
       </c>
       <c r="D61" t="n">
-        <v>2038.72</v>
+        <v>1761.68</v>
       </c>
       <c r="E61" t="n">
-        <v>1804.18</v>
+        <v>1559.01</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -2201,24 +2201,24 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2628.75</v>
+        <v>3112.33</v>
       </c>
       <c r="D62" t="n">
-        <v>2970.49</v>
+        <v>3516.93</v>
       </c>
       <c r="E62" t="n">
-        <v>2628.75</v>
+        <v>3112.33</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -2234,20 +2234,20 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4909.72</v>
+        <v>1570.44</v>
       </c>
       <c r="D63" t="n">
-        <v>5547.98</v>
+        <v>1774.6</v>
       </c>
       <c r="E63" t="n">
-        <v>4909.72</v>
+        <v>1570.44</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -2259,24 +2259,24 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>649.78</v>
+        <v>3765.05</v>
       </c>
       <c r="D64" t="n">
-        <v>734.25</v>
+        <v>4254.51</v>
       </c>
       <c r="E64" t="n">
-        <v>649.78</v>
+        <v>3765.05</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -2288,24 +2288,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2451.43</v>
+        <v>859.12</v>
       </c>
       <c r="D65" t="n">
-        <v>2770.12</v>
+        <v>970.8099999999999</v>
       </c>
       <c r="E65" t="n">
-        <v>2451.43</v>
+        <v>859.12</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
     </row>
@@ -2317,24 +2317,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3553.21</v>
+        <v>411.16</v>
       </c>
       <c r="D66" t="n">
-        <v>4015.13</v>
+        <v>464.61</v>
       </c>
       <c r="E66" t="n">
-        <v>3553.21</v>
+        <v>411.16</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
@@ -2350,20 +2350,20 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>660.29</v>
+        <v>1824.47</v>
       </c>
       <c r="D67" t="n">
-        <v>746.13</v>
+        <v>2061.65</v>
       </c>
       <c r="E67" t="n">
-        <v>660.29</v>
+        <v>1824.47</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
@@ -2379,20 +2379,20 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>4362.7</v>
+        <v>2498.34</v>
       </c>
       <c r="D68" t="n">
-        <v>4929.85</v>
+        <v>2823.12</v>
       </c>
       <c r="E68" t="n">
-        <v>4362.7</v>
+        <v>2498.34</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-06-28</t>
         </is>
       </c>
     </row>
@@ -2404,24 +2404,24 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3232.35</v>
+        <v>4657.58</v>
       </c>
       <c r="D69" t="n">
-        <v>3652.56</v>
+        <v>5263.07</v>
       </c>
       <c r="E69" t="n">
-        <v>3232.35</v>
+        <v>4657.58</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
@@ -2433,24 +2433,24 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3179.65</v>
+        <v>3352.62</v>
       </c>
       <c r="D70" t="n">
-        <v>3593</v>
+        <v>3788.46</v>
       </c>
       <c r="E70" t="n">
-        <v>3179.65</v>
+        <v>3352.62</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-07</t>
         </is>
       </c>
     </row>
@@ -2462,24 +2462,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1624.79</v>
+        <v>738.92</v>
       </c>
       <c r="D71" t="n">
-        <v>1836.01</v>
+        <v>834.98</v>
       </c>
       <c r="E71" t="n">
-        <v>1624.79</v>
+        <v>738.92</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-07-12</t>
         </is>
       </c>
     </row>
@@ -2491,24 +2491,24 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>616.65</v>
+        <v>4180.06</v>
       </c>
       <c r="D72" t="n">
-        <v>696.8099999999999</v>
+        <v>4723.47</v>
       </c>
       <c r="E72" t="n">
-        <v>575.74</v>
+        <v>4180.06</v>
       </c>
       <c r="F72" t="n">
-        <v>40.91</v>
+        <v>0</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -2524,20 +2524,20 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1023.51</v>
+        <v>1999.84</v>
       </c>
       <c r="D73" t="n">
-        <v>1156.57</v>
+        <v>2259.82</v>
       </c>
       <c r="E73" t="n">
-        <v>1023.51</v>
+        <v>1999.84</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -2549,24 +2549,24 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>270.96</v>
+        <v>3377.11</v>
       </c>
       <c r="D74" t="n">
-        <v>306.18</v>
+        <v>3816.13</v>
       </c>
       <c r="E74" t="n">
-        <v>270.96</v>
+        <v>3377.11</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -2578,24 +2578,24 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>4620.44</v>
+        <v>4049.63</v>
       </c>
       <c r="D75" t="n">
-        <v>5221.1</v>
+        <v>4576.08</v>
       </c>
       <c r="E75" t="n">
-        <v>4620.44</v>
+        <v>3905.5</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>144.13</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
     </row>
@@ -2607,17 +2607,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>4353.86</v>
+        <v>4182.85</v>
       </c>
       <c r="D76" t="n">
-        <v>4919.86</v>
+        <v>4726.62</v>
       </c>
       <c r="E76" t="n">
-        <v>4353.86</v>
+        <v>4182.85</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -2640,20 +2640,20 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3603.75</v>
+        <v>3588.96</v>
       </c>
       <c r="D77" t="n">
-        <v>4072.24</v>
+        <v>4055.52</v>
       </c>
       <c r="E77" t="n">
-        <v>3157</v>
+        <v>3588.96</v>
       </c>
       <c r="F77" t="n">
-        <v>446.75</v>
+        <v>0</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -2665,24 +2665,24 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>4792.12</v>
+        <v>3796.99</v>
       </c>
       <c r="D78" t="n">
-        <v>5415.1</v>
+        <v>4290.6</v>
       </c>
       <c r="E78" t="n">
-        <v>4792.12</v>
+        <v>3796.99</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -2694,24 +2694,24 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>167.93</v>
+        <v>441.88</v>
       </c>
       <c r="D79" t="n">
-        <v>189.76</v>
+        <v>499.32</v>
       </c>
       <c r="E79" t="n">
-        <v>167.93</v>
+        <v>441.88</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
@@ -2727,20 +2727,20 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>4056.53</v>
+        <v>3860.43</v>
       </c>
       <c r="D80" t="n">
-        <v>4583.88</v>
+        <v>4362.29</v>
       </c>
       <c r="E80" t="n">
-        <v>4056.53</v>
+        <v>3860.43</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2752,24 +2752,24 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2536.42</v>
+        <v>3535.3</v>
       </c>
       <c r="D81" t="n">
-        <v>2866.15</v>
+        <v>3994.89</v>
       </c>
       <c r="E81" t="n">
-        <v>2536.42</v>
+        <v>3535.3</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -2785,20 +2785,20 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2060.39</v>
+        <v>4953.77</v>
       </c>
       <c r="D82" t="n">
-        <v>2328.24</v>
+        <v>5597.76</v>
       </c>
       <c r="E82" t="n">
-        <v>2060.39</v>
+        <v>4953.77</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -2810,20 +2810,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3260.94</v>
+        <v>4257</v>
       </c>
       <c r="D83" t="n">
-        <v>3684.86</v>
+        <v>4810.41</v>
       </c>
       <c r="E83" t="n">
-        <v>3260.94</v>
+        <v>3842.32</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>414.68</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -2839,24 +2839,24 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>782.28</v>
+        <v>2227.85</v>
       </c>
       <c r="D84" t="n">
-        <v>883.98</v>
+        <v>2517.47</v>
       </c>
       <c r="E84" t="n">
-        <v>782.28</v>
+        <v>2227.85</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
@@ -2868,24 +2868,24 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>228.63</v>
+        <v>2902.95</v>
       </c>
       <c r="D85" t="n">
-        <v>258.35</v>
+        <v>3280.33</v>
       </c>
       <c r="E85" t="n">
-        <v>228.63</v>
+        <v>2902.95</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -2897,24 +2897,24 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>741.37</v>
+        <v>1878.05</v>
       </c>
       <c r="D86" t="n">
-        <v>837.75</v>
+        <v>2122.2</v>
       </c>
       <c r="E86" t="n">
-        <v>630.75</v>
+        <v>1878.05</v>
       </c>
       <c r="F86" t="n">
-        <v>110.62</v>
+        <v>0</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -2926,24 +2926,24 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2605.99</v>
+        <v>2177.97</v>
       </c>
       <c r="D87" t="n">
-        <v>2944.77</v>
+        <v>2461.11</v>
       </c>
       <c r="E87" t="n">
-        <v>2605.99</v>
+        <v>1744.31</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>433.66</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -2955,24 +2955,24 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3604.57</v>
+        <v>2175.75</v>
       </c>
       <c r="D88" t="n">
-        <v>4073.16</v>
+        <v>2458.6</v>
       </c>
       <c r="E88" t="n">
-        <v>3604.57</v>
+        <v>2175.75</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2984,24 +2984,24 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3418.58</v>
+        <v>4001.08</v>
       </c>
       <c r="D89" t="n">
-        <v>3863</v>
+        <v>4521.22</v>
       </c>
       <c r="E89" t="n">
-        <v>3418.58</v>
+        <v>4001.08</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
@@ -3017,20 +3017,20 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2839.6</v>
+        <v>1661.64</v>
       </c>
       <c r="D90" t="n">
-        <v>3208.75</v>
+        <v>1877.65</v>
       </c>
       <c r="E90" t="n">
-        <v>2839.6</v>
+        <v>1661.64</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -3042,24 +3042,24 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2055.11</v>
+        <v>1475.97</v>
       </c>
       <c r="D91" t="n">
-        <v>2322.27</v>
+        <v>1667.85</v>
       </c>
       <c r="E91" t="n">
-        <v>2055.11</v>
+        <v>1475.97</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -3071,24 +3071,24 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>654.8200000000001</v>
+        <v>4074.66</v>
       </c>
       <c r="D92" t="n">
-        <v>739.95</v>
+        <v>4604.37</v>
       </c>
       <c r="E92" t="n">
-        <v>534.87</v>
+        <v>4074.66</v>
       </c>
       <c r="F92" t="n">
-        <v>119.95</v>
+        <v>0</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -3104,20 +3104,20 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>458.63</v>
+        <v>4822.21</v>
       </c>
       <c r="D93" t="n">
-        <v>518.25</v>
+        <v>5449.1</v>
       </c>
       <c r="E93" t="n">
-        <v>458.63</v>
+        <v>4822.21</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -3133,20 +3133,20 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>197.99</v>
+        <v>4209.94</v>
       </c>
       <c r="D94" t="n">
-        <v>223.73</v>
+        <v>4757.23</v>
       </c>
       <c r="E94" t="n">
-        <v>197.99</v>
+        <v>4209.94</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -3162,20 +3162,20 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>138.13</v>
+        <v>2173.57</v>
       </c>
       <c r="D95" t="n">
-        <v>156.09</v>
+        <v>2456.13</v>
       </c>
       <c r="E95" t="n">
-        <v>138.13</v>
+        <v>2173.57</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -3191,20 +3191,20 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>191.56</v>
+        <v>1600.69</v>
       </c>
       <c r="D96" t="n">
-        <v>216.46</v>
+        <v>1808.78</v>
       </c>
       <c r="E96" t="n">
-        <v>191.56</v>
+        <v>1600.69</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-28</t>
         </is>
       </c>
     </row>
@@ -3216,24 +3216,24 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>4712.14</v>
+        <v>2307.28</v>
       </c>
       <c r="D97" t="n">
-        <v>5324.72</v>
+        <v>2607.23</v>
       </c>
       <c r="E97" t="n">
-        <v>4712.14</v>
+        <v>2307.28</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
@@ -3245,24 +3245,24 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>734.7</v>
+        <v>1840.83</v>
       </c>
       <c r="D98" t="n">
-        <v>830.21</v>
+        <v>2080.14</v>
       </c>
       <c r="E98" t="n">
-        <v>650.46</v>
+        <v>1840.83</v>
       </c>
       <c r="F98" t="n">
-        <v>84.23999999999999</v>
+        <v>0</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
@@ -3278,20 +3278,20 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2277.53</v>
+        <v>1107.7</v>
       </c>
       <c r="D99" t="n">
-        <v>2573.61</v>
+        <v>1251.7</v>
       </c>
       <c r="E99" t="n">
-        <v>2277.53</v>
+        <v>1107.7</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -3303,24 +3303,24 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>800.53</v>
+        <v>3077.15</v>
       </c>
       <c r="D100" t="n">
-        <v>904.6</v>
+        <v>3477.18</v>
       </c>
       <c r="E100" t="n">
-        <v>651.92</v>
+        <v>3077.15</v>
       </c>
       <c r="F100" t="n">
-        <v>148.61</v>
+        <v>0</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
@@ -3332,24 +3332,24 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2296.87</v>
+        <v>3639.77</v>
       </c>
       <c r="D101" t="n">
-        <v>2595.46</v>
+        <v>4112.94</v>
       </c>
       <c r="E101" t="n">
-        <v>2296.87</v>
+        <v>3639.77</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -3361,24 +3361,24 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>367.23</v>
+        <v>1573.04</v>
       </c>
       <c r="D102" t="n">
-        <v>414.97</v>
+        <v>1777.54</v>
       </c>
       <c r="E102" t="n">
-        <v>367.23</v>
+        <v>1573.04</v>
       </c>
       <c r="F102" t="n">
         <v>0</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
@@ -3390,24 +3390,24 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1407.15</v>
+        <v>1212.03</v>
       </c>
       <c r="D103" t="n">
-        <v>1590.08</v>
+        <v>1369.59</v>
       </c>
       <c r="E103" t="n">
-        <v>1305.57</v>
+        <v>1212.03</v>
       </c>
       <c r="F103" t="n">
-        <v>101.58</v>
+        <v>0</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
@@ -3419,24 +3419,24 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>290.19</v>
+        <v>4575.47</v>
       </c>
       <c r="D104" t="n">
-        <v>327.91</v>
+        <v>5170.28</v>
       </c>
       <c r="E104" t="n">
-        <v>263.34</v>
+        <v>4575.47</v>
       </c>
       <c r="F104" t="n">
-        <v>26.85</v>
+        <v>0</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -3452,20 +3452,20 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3686.3</v>
+        <v>313.94</v>
       </c>
       <c r="D105" t="n">
-        <v>4165.52</v>
+        <v>354.75</v>
       </c>
       <c r="E105" t="n">
-        <v>3686.3</v>
+        <v>313.94</v>
       </c>
       <c r="F105" t="n">
         <v>0</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -3481,20 +3481,20 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2679.91</v>
+        <v>2124.77</v>
       </c>
       <c r="D106" t="n">
-        <v>3028.3</v>
+        <v>2400.99</v>
       </c>
       <c r="E106" t="n">
-        <v>2533.15</v>
+        <v>2124.77</v>
       </c>
       <c r="F106" t="n">
-        <v>146.76</v>
+        <v>0</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -3506,24 +3506,24 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4239.09</v>
+        <v>350.51</v>
       </c>
       <c r="D107" t="n">
-        <v>4790.17</v>
+        <v>396.08</v>
       </c>
       <c r="E107" t="n">
-        <v>4239.09</v>
+        <v>298.38</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>52.13</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
@@ -3539,20 +3539,20 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1481.75</v>
+        <v>2544.2</v>
       </c>
       <c r="D108" t="n">
-        <v>1674.38</v>
+        <v>2874.95</v>
       </c>
       <c r="E108" t="n">
-        <v>1481.75</v>
+        <v>2544.2</v>
       </c>
       <c r="F108" t="n">
         <v>0</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
@@ -3564,24 +3564,24 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1496.94</v>
+        <v>1713.03</v>
       </c>
       <c r="D109" t="n">
-        <v>1691.54</v>
+        <v>1935.72</v>
       </c>
       <c r="E109" t="n">
-        <v>1496.94</v>
+        <v>1713.03</v>
       </c>
       <c r="F109" t="n">
         <v>0</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
@@ -3593,24 +3593,24 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1390.81</v>
+        <v>4327.76</v>
       </c>
       <c r="D110" t="n">
-        <v>1571.62</v>
+        <v>4890.37</v>
       </c>
       <c r="E110" t="n">
-        <v>1163.48</v>
+        <v>4327.76</v>
       </c>
       <c r="F110" t="n">
-        <v>227.33</v>
+        <v>0</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
@@ -3622,24 +3622,24 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>3090.31</v>
+        <v>3043.11</v>
       </c>
       <c r="D111" t="n">
-        <v>3492.05</v>
+        <v>3438.71</v>
       </c>
       <c r="E111" t="n">
-        <v>3090.31</v>
+        <v>2867.12</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>175.99</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
@@ -3651,24 +3651,24 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1932.25</v>
+        <v>3554.88</v>
       </c>
       <c r="D112" t="n">
-        <v>2183.44</v>
+        <v>4017.01</v>
       </c>
       <c r="E112" t="n">
-        <v>1932.25</v>
+        <v>3554.88</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
@@ -3680,24 +3680,24 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2392.11</v>
+        <v>1892.7</v>
       </c>
       <c r="D113" t="n">
-        <v>2703.08</v>
+        <v>2138.75</v>
       </c>
       <c r="E113" t="n">
-        <v>2392.11</v>
+        <v>1769.36</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>123.34</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -3709,24 +3709,24 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>2502.14</v>
+        <v>1092.62</v>
       </c>
       <c r="D114" t="n">
-        <v>2827.42</v>
+        <v>1234.66</v>
       </c>
       <c r="E114" t="n">
-        <v>2502.14</v>
+        <v>1092.62</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -3738,24 +3738,24 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>3496.42</v>
+        <v>4531.12</v>
       </c>
       <c r="D115" t="n">
-        <v>3950.95</v>
+        <v>5120.17</v>
       </c>
       <c r="E115" t="n">
-        <v>3496.42</v>
+        <v>4531.12</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-05</t>
         </is>
       </c>
     </row>
@@ -3767,24 +3767,24 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1435.76</v>
+        <v>2579.21</v>
       </c>
       <c r="D116" t="n">
-        <v>1622.41</v>
+        <v>2914.51</v>
       </c>
       <c r="E116" t="n">
-        <v>1435.76</v>
+        <v>2579.21</v>
       </c>
       <c r="F116" t="n">
         <v>0</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -3796,24 +3796,24 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>2039.24</v>
+        <v>4513.15</v>
       </c>
       <c r="D117" t="n">
-        <v>2304.34</v>
+        <v>5099.86</v>
       </c>
       <c r="E117" t="n">
-        <v>2039.24</v>
+        <v>4513.15</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -3825,24 +3825,24 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1466.19</v>
+        <v>1386.93</v>
       </c>
       <c r="D118" t="n">
-        <v>1656.79</v>
+        <v>1567.23</v>
       </c>
       <c r="E118" t="n">
-        <v>1466.19</v>
+        <v>1386.93</v>
       </c>
       <c r="F118" t="n">
         <v>0</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
@@ -3858,20 +3858,20 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>3241.67</v>
+        <v>918.8200000000001</v>
       </c>
       <c r="D119" t="n">
-        <v>3663.09</v>
+        <v>1038.27</v>
       </c>
       <c r="E119" t="n">
-        <v>3241.67</v>
+        <v>918.8200000000001</v>
       </c>
       <c r="F119" t="n">
         <v>0</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -3887,20 +3887,20 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>3047.71</v>
+        <v>4486.87</v>
       </c>
       <c r="D120" t="n">
-        <v>3443.91</v>
+        <v>5070.16</v>
       </c>
       <c r="E120" t="n">
-        <v>3047.71</v>
+        <v>3964.54</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>522.33</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
@@ -3912,24 +3912,24 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1821.53</v>
+        <v>3139.76</v>
       </c>
       <c r="D121" t="n">
-        <v>2058.33</v>
+        <v>3547.93</v>
       </c>
       <c r="E121" t="n">
-        <v>1821.53</v>
+        <v>3139.76</v>
       </c>
       <c r="F121" t="n">
         <v>0</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-07</t>
         </is>
       </c>
     </row>
@@ -3941,24 +3941,24 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1661.47</v>
+        <v>807.75</v>
       </c>
       <c r="D122" t="n">
-        <v>1877.46</v>
+        <v>912.76</v>
       </c>
       <c r="E122" t="n">
-        <v>1661.47</v>
+        <v>739.4299999999999</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -3970,24 +3970,24 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>3866.47</v>
+        <v>804.88</v>
       </c>
       <c r="D123" t="n">
-        <v>4369.11</v>
+        <v>909.51</v>
       </c>
       <c r="E123" t="n">
-        <v>3866.47</v>
+        <v>755.46</v>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>49.42</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -3999,24 +3999,24 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1803.22</v>
+        <v>329.67</v>
       </c>
       <c r="D124" t="n">
-        <v>2037.64</v>
+        <v>372.53</v>
       </c>
       <c r="E124" t="n">
-        <v>1699.92</v>
+        <v>329.67</v>
       </c>
       <c r="F124" t="n">
-        <v>103.3</v>
+        <v>0</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
@@ -4028,24 +4028,24 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>708.45</v>
+        <v>1760.65</v>
       </c>
       <c r="D125" t="n">
-        <v>800.55</v>
+        <v>1989.53</v>
       </c>
       <c r="E125" t="n">
-        <v>708.45</v>
+        <v>1760.65</v>
       </c>
       <c r="F125" t="n">
         <v>0</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
@@ -4057,24 +4057,24 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1024.87</v>
+        <v>2260.96</v>
       </c>
       <c r="D126" t="n">
-        <v>1158.1</v>
+        <v>2554.88</v>
       </c>
       <c r="E126" t="n">
-        <v>1024.87</v>
+        <v>2260.96</v>
       </c>
       <c r="F126" t="n">
         <v>0</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4090,20 +4090,20 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>773.78</v>
+        <v>4707.29</v>
       </c>
       <c r="D127" t="n">
-        <v>874.37</v>
+        <v>5319.24</v>
       </c>
       <c r="E127" t="n">
-        <v>773.78</v>
+        <v>4707.29</v>
       </c>
       <c r="F127" t="n">
         <v>0</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -4119,20 +4119,20 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>118.85</v>
+        <v>183.06</v>
       </c>
       <c r="D128" t="n">
-        <v>134.3</v>
+        <v>206.86</v>
       </c>
       <c r="E128" t="n">
-        <v>107.84</v>
+        <v>183.06</v>
       </c>
       <c r="F128" t="n">
-        <v>11.01</v>
+        <v>0</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -4144,24 +4144,24 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>4685.42</v>
+        <v>1492.03</v>
       </c>
       <c r="D129" t="n">
-        <v>5294.52</v>
+        <v>1685.99</v>
       </c>
       <c r="E129" t="n">
-        <v>4685.42</v>
+        <v>1492.03</v>
       </c>
       <c r="F129" t="n">
         <v>0</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -4177,20 +4177,20 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>846.23</v>
+        <v>2467.88</v>
       </c>
       <c r="D130" t="n">
-        <v>956.24</v>
+        <v>2788.7</v>
       </c>
       <c r="E130" t="n">
-        <v>846.23</v>
+        <v>2463.99</v>
       </c>
       <c r="F130" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -4206,20 +4206,20 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>2730.49</v>
+        <v>1775.33</v>
       </c>
       <c r="D131" t="n">
-        <v>3085.45</v>
+        <v>2006.12</v>
       </c>
       <c r="E131" t="n">
-        <v>2730.49</v>
+        <v>1775.33</v>
       </c>
       <c r="F131" t="n">
         <v>0</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-12</t>
         </is>
       </c>
     </row>
@@ -4231,24 +4231,24 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>847.47</v>
+        <v>2592.31</v>
       </c>
       <c r="D132" t="n">
-        <v>957.64</v>
+        <v>2929.31</v>
       </c>
       <c r="E132" t="n">
-        <v>847.47</v>
+        <v>2592.31</v>
       </c>
       <c r="F132" t="n">
         <v>0</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -4260,24 +4260,24 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1805.67</v>
+        <v>3368.35</v>
       </c>
       <c r="D133" t="n">
-        <v>2040.41</v>
+        <v>3806.24</v>
       </c>
       <c r="E133" t="n">
-        <v>1805.67</v>
+        <v>3368.35</v>
       </c>
       <c r="F133" t="n">
         <v>0</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
@@ -4289,24 +4289,24 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>3907.38</v>
+        <v>756.63</v>
       </c>
       <c r="D134" t="n">
-        <v>4415.34</v>
+        <v>854.99</v>
       </c>
       <c r="E134" t="n">
-        <v>3907.38</v>
+        <v>756.63</v>
       </c>
       <c r="F134" t="n">
         <v>0</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -4318,24 +4318,24 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>3992.7</v>
+        <v>4505.74</v>
       </c>
       <c r="D135" t="n">
-        <v>4511.75</v>
+        <v>5091.49</v>
       </c>
       <c r="E135" t="n">
-        <v>3992.7</v>
+        <v>4505.74</v>
       </c>
       <c r="F135" t="n">
         <v>0</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -4347,24 +4347,24 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>4968.01</v>
+        <v>3700.81</v>
       </c>
       <c r="D136" t="n">
-        <v>5613.85</v>
+        <v>4181.92</v>
       </c>
       <c r="E136" t="n">
-        <v>4968.01</v>
+        <v>3419.14</v>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
+        <v>281.67</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
     </row>
@@ -4376,24 +4376,24 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>2539.22</v>
+        <v>1035.05</v>
       </c>
       <c r="D137" t="n">
-        <v>2869.32</v>
+        <v>1169.61</v>
       </c>
       <c r="E137" t="n">
-        <v>2539.22</v>
+        <v>1035.05</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
@@ -4405,24 +4405,24 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>436.12</v>
+        <v>1037.96</v>
       </c>
       <c r="D138" t="n">
-        <v>492.82</v>
+        <v>1172.89</v>
       </c>
       <c r="E138" t="n">
-        <v>436.12</v>
+        <v>1037.96</v>
       </c>
       <c r="F138" t="n">
         <v>0</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
@@ -4434,24 +4434,24 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>2939.6</v>
+        <v>3806.43</v>
       </c>
       <c r="D139" t="n">
-        <v>3321.75</v>
+        <v>4301.27</v>
       </c>
       <c r="E139" t="n">
-        <v>2939.6</v>
+        <v>3806.43</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -4463,24 +4463,24 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>962.28</v>
+        <v>2766.57</v>
       </c>
       <c r="D140" t="n">
-        <v>1087.38</v>
+        <v>3126.22</v>
       </c>
       <c r="E140" t="n">
-        <v>962.28</v>
+        <v>2766.57</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -4492,24 +4492,24 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>3792.45</v>
+        <v>254.12</v>
       </c>
       <c r="D141" t="n">
-        <v>4285.47</v>
+        <v>287.16</v>
       </c>
       <c r="E141" t="n">
-        <v>3792.45</v>
+        <v>254.12</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -4521,24 +4521,24 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1963.1</v>
+        <v>484.05</v>
       </c>
       <c r="D142" t="n">
-        <v>2218.3</v>
+        <v>546.98</v>
       </c>
       <c r="E142" t="n">
-        <v>1963.1</v>
+        <v>445.9</v>
       </c>
       <c r="F142" t="n">
-        <v>0</v>
+        <v>38.15</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -4550,24 +4550,24 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>3009.26</v>
+        <v>1377.51</v>
       </c>
       <c r="D143" t="n">
-        <v>3400.46</v>
+        <v>1556.59</v>
       </c>
       <c r="E143" t="n">
-        <v>2825.36</v>
+        <v>1377.51</v>
       </c>
       <c r="F143" t="n">
-        <v>183.9</v>
+        <v>0</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -4579,24 +4579,24 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>212.38</v>
+        <v>4656.29</v>
       </c>
       <c r="D144" t="n">
-        <v>239.99</v>
+        <v>5261.61</v>
       </c>
       <c r="E144" t="n">
-        <v>212.38</v>
+        <v>4643.35</v>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>12.94</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -4612,20 +4612,20 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>4385.81</v>
+        <v>4340.29</v>
       </c>
       <c r="D145" t="n">
-        <v>4955.97</v>
+        <v>4904.53</v>
       </c>
       <c r="E145" t="n">
-        <v>4385.81</v>
+        <v>4340.29</v>
       </c>
       <c r="F145" t="n">
         <v>0</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -4637,24 +4637,24 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>2303.55</v>
+        <v>2041.37</v>
       </c>
       <c r="D146" t="n">
-        <v>2603.01</v>
+        <v>2306.75</v>
       </c>
       <c r="E146" t="n">
-        <v>2303.55</v>
+        <v>2041.37</v>
       </c>
       <c r="F146" t="n">
         <v>0</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
@@ -4666,24 +4666,24 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>4493.74</v>
+        <v>3868.39</v>
       </c>
       <c r="D147" t="n">
-        <v>5077.93</v>
+        <v>4371.28</v>
       </c>
       <c r="E147" t="n">
-        <v>4493.74</v>
+        <v>3868.39</v>
       </c>
       <c r="F147" t="n">
         <v>0</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
@@ -4695,24 +4695,24 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>433.39</v>
+        <v>4978.34</v>
       </c>
       <c r="D148" t="n">
-        <v>489.73</v>
+        <v>5625.52</v>
       </c>
       <c r="E148" t="n">
-        <v>433.39</v>
+        <v>4978.34</v>
       </c>
       <c r="F148" t="n">
         <v>0</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
@@ -4724,24 +4724,24 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>749.38</v>
+        <v>546.03</v>
       </c>
       <c r="D149" t="n">
-        <v>846.8</v>
+        <v>617.01</v>
       </c>
       <c r="E149" t="n">
-        <v>749.38</v>
+        <v>538.66</v>
       </c>
       <c r="F149" t="n">
-        <v>0</v>
+        <v>7.37</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-06-21</t>
         </is>
       </c>
     </row>
@@ -4757,20 +4757,20 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>3618.82</v>
+        <v>3117.86</v>
       </c>
       <c r="D150" t="n">
-        <v>4089.27</v>
+        <v>3523.18</v>
       </c>
       <c r="E150" t="n">
-        <v>3618.82</v>
+        <v>2663.48</v>
       </c>
       <c r="F150" t="n">
-        <v>0</v>
+        <v>454.38</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
@@ -4786,20 +4786,20 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>4905.85</v>
+        <v>264.99</v>
       </c>
       <c r="D151" t="n">
-        <v>5543.61</v>
+        <v>299.44</v>
       </c>
       <c r="E151" t="n">
-        <v>4905.85</v>
+        <v>264.99</v>
       </c>
       <c r="F151" t="n">
         <v>0</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -4815,20 +4815,20 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>2045.52</v>
+        <v>1118.17</v>
       </c>
       <c r="D152" t="n">
-        <v>2311.44</v>
+        <v>1263.53</v>
       </c>
       <c r="E152" t="n">
-        <v>2045.52</v>
+        <v>1118.17</v>
       </c>
       <c r="F152" t="n">
         <v>0</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
@@ -4844,20 +4844,20 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>3491.09</v>
+        <v>4801.94</v>
       </c>
       <c r="D153" t="n">
-        <v>3944.93</v>
+        <v>5426.19</v>
       </c>
       <c r="E153" t="n">
-        <v>3491.09</v>
+        <v>4801.94</v>
       </c>
       <c r="F153" t="n">
         <v>0</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
@@ -4869,24 +4869,24 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1559.97</v>
+        <v>1551.39</v>
       </c>
       <c r="D154" t="n">
-        <v>1762.77</v>
+        <v>1753.07</v>
       </c>
       <c r="E154" t="n">
-        <v>1559.97</v>
+        <v>1551.39</v>
       </c>
       <c r="F154" t="n">
         <v>0</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -4902,20 +4902,20 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>2454.96</v>
+        <v>478.47</v>
       </c>
       <c r="D155" t="n">
-        <v>2774.1</v>
+        <v>540.67</v>
       </c>
       <c r="E155" t="n">
-        <v>2454.96</v>
+        <v>451.56</v>
       </c>
       <c r="F155" t="n">
-        <v>0</v>
+        <v>26.91</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -4927,24 +4927,24 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1893.04</v>
+        <v>4248.96</v>
       </c>
       <c r="D156" t="n">
-        <v>2139.14</v>
+        <v>4801.32</v>
       </c>
       <c r="E156" t="n">
-        <v>1893.04</v>
+        <v>4248.96</v>
       </c>
       <c r="F156" t="n">
         <v>0</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -4956,24 +4956,24 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>190.45</v>
+        <v>2962.95</v>
       </c>
       <c r="D157" t="n">
-        <v>215.21</v>
+        <v>3348.13</v>
       </c>
       <c r="E157" t="n">
-        <v>190.45</v>
+        <v>2962.95</v>
       </c>
       <c r="F157" t="n">
         <v>0</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
@@ -4989,20 +4989,20 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1918.34</v>
+        <v>3870.28</v>
       </c>
       <c r="D158" t="n">
-        <v>2167.72</v>
+        <v>4373.42</v>
       </c>
       <c r="E158" t="n">
-        <v>1918.34</v>
+        <v>3870.28</v>
       </c>
       <c r="F158" t="n">
         <v>0</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -5014,24 +5014,24 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>3983.61</v>
+        <v>3109.17</v>
       </c>
       <c r="D159" t="n">
-        <v>4501.48</v>
+        <v>3513.36</v>
       </c>
       <c r="E159" t="n">
-        <v>3983.61</v>
+        <v>3109.17</v>
       </c>
       <c r="F159" t="n">
         <v>0</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
@@ -5047,20 +5047,20 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1094.48</v>
+        <v>1611.29</v>
       </c>
       <c r="D160" t="n">
-        <v>1236.76</v>
+        <v>1820.76</v>
       </c>
       <c r="E160" t="n">
-        <v>1094.48</v>
+        <v>1611.29</v>
       </c>
       <c r="F160" t="n">
         <v>0</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -5072,24 +5072,24 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>4952.94</v>
+        <v>3852.59</v>
       </c>
       <c r="D161" t="n">
-        <v>5596.82</v>
+        <v>4353.43</v>
       </c>
       <c r="E161" t="n">
-        <v>4660.39</v>
+        <v>3852.59</v>
       </c>
       <c r="F161" t="n">
-        <v>292.55</v>
+        <v>0</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -5101,24 +5101,24 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>4416.01</v>
+        <v>4742.22</v>
       </c>
       <c r="D162" t="n">
-        <v>4990.09</v>
+        <v>5358.71</v>
       </c>
       <c r="E162" t="n">
-        <v>4376.71</v>
+        <v>3824.06</v>
       </c>
       <c r="F162" t="n">
-        <v>39.3</v>
+        <v>918.16</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5130,24 +5130,24 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1947.63</v>
+        <v>319.4</v>
       </c>
       <c r="D163" t="n">
-        <v>2200.82</v>
+        <v>360.92</v>
       </c>
       <c r="E163" t="n">
-        <v>1947.63</v>
+        <v>319.4</v>
       </c>
       <c r="F163" t="n">
         <v>0</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -5159,17 +5159,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>3655.8</v>
+        <v>728.92</v>
       </c>
       <c r="D164" t="n">
-        <v>4131.05</v>
+        <v>823.6799999999999</v>
       </c>
       <c r="E164" t="n">
-        <v>3655.8</v>
+        <v>728.92</v>
       </c>
       <c r="F164" t="n">
         <v>0</v>
@@ -5188,24 +5188,24 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>4142.61</v>
+        <v>4560.89</v>
       </c>
       <c r="D165" t="n">
-        <v>4681.15</v>
+        <v>5153.81</v>
       </c>
       <c r="E165" t="n">
-        <v>4142.61</v>
+        <v>4560.89</v>
       </c>
       <c r="F165" t="n">
         <v>0</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -5217,24 +5217,24 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1613.68</v>
+        <v>1606.81</v>
       </c>
       <c r="D166" t="n">
-        <v>1823.46</v>
+        <v>1815.7</v>
       </c>
       <c r="E166" t="n">
-        <v>1613.68</v>
+        <v>1606.81</v>
       </c>
       <c r="F166" t="n">
         <v>0</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5250,13 +5250,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>655.59</v>
+        <v>1333.68</v>
       </c>
       <c r="D167" t="n">
-        <v>740.8200000000001</v>
+        <v>1507.06</v>
       </c>
       <c r="E167" t="n">
-        <v>655.59</v>
+        <v>1333.68</v>
       </c>
       <c r="F167" t="n">
         <v>0</v>
@@ -5275,24 +5275,24 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>2754.19</v>
+        <v>4619.59</v>
       </c>
       <c r="D168" t="n">
-        <v>3112.23</v>
+        <v>5220.14</v>
       </c>
       <c r="E168" t="n">
-        <v>2754.19</v>
+        <v>4619.59</v>
       </c>
       <c r="F168" t="n">
         <v>0</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
@@ -5304,24 +5304,24 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>253.84</v>
+        <v>3535.04</v>
       </c>
       <c r="D169" t="n">
-        <v>286.84</v>
+        <v>3994.6</v>
       </c>
       <c r="E169" t="n">
-        <v>253.84</v>
+        <v>3535.04</v>
       </c>
       <c r="F169" t="n">
         <v>0</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
@@ -5333,24 +5333,24 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>4394.26</v>
+        <v>2242.42</v>
       </c>
       <c r="D170" t="n">
-        <v>4965.51</v>
+        <v>2533.93</v>
       </c>
       <c r="E170" t="n">
-        <v>4394.26</v>
+        <v>2242.42</v>
       </c>
       <c r="F170" t="n">
         <v>0</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -5366,20 +5366,20 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1563.51</v>
+        <v>4013.52</v>
       </c>
       <c r="D171" t="n">
-        <v>1766.77</v>
+        <v>4535.28</v>
       </c>
       <c r="E171" t="n">
-        <v>1563.51</v>
+        <v>4013.52</v>
       </c>
       <c r="F171" t="n">
         <v>0</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -5391,24 +5391,24 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>2822.5</v>
+        <v>1558.59</v>
       </c>
       <c r="D172" t="n">
-        <v>3189.42</v>
+        <v>1761.21</v>
       </c>
       <c r="E172" t="n">
-        <v>2822.5</v>
+        <v>1558.59</v>
       </c>
       <c r="F172" t="n">
         <v>0</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -5424,20 +5424,20 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>2114.26</v>
+        <v>3482.91</v>
       </c>
       <c r="D173" t="n">
-        <v>2389.11</v>
+        <v>3935.69</v>
       </c>
       <c r="E173" t="n">
-        <v>2114.26</v>
+        <v>3482.91</v>
       </c>
       <c r="F173" t="n">
         <v>0</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -5453,20 +5453,20 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>4091.65</v>
+        <v>4305.6</v>
       </c>
       <c r="D174" t="n">
-        <v>4623.56</v>
+        <v>4865.33</v>
       </c>
       <c r="E174" t="n">
-        <v>4091.65</v>
+        <v>4305.6</v>
       </c>
       <c r="F174" t="n">
         <v>0</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -5478,24 +5478,24 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>3712.05</v>
+        <v>4984.83</v>
       </c>
       <c r="D175" t="n">
-        <v>4194.62</v>
+        <v>5632.86</v>
       </c>
       <c r="E175" t="n">
-        <v>3712.05</v>
+        <v>4984.83</v>
       </c>
       <c r="F175" t="n">
         <v>0</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
@@ -5507,24 +5507,24 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>980.85</v>
+        <v>4495.8</v>
       </c>
       <c r="D176" t="n">
-        <v>1108.36</v>
+        <v>5080.25</v>
       </c>
       <c r="E176" t="n">
-        <v>980.85</v>
+        <v>4495.8</v>
       </c>
       <c r="F176" t="n">
         <v>0</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
@@ -5536,24 +5536,24 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1973.22</v>
+        <v>3214.17</v>
       </c>
       <c r="D177" t="n">
-        <v>2229.74</v>
+        <v>3632.01</v>
       </c>
       <c r="E177" t="n">
-        <v>1973.22</v>
+        <v>2936.77</v>
       </c>
       <c r="F177" t="n">
-        <v>0</v>
+        <v>277.4</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -5565,24 +5565,24 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>2507.42</v>
+        <v>2343.03</v>
       </c>
       <c r="D178" t="n">
-        <v>2833.38</v>
+        <v>2647.62</v>
       </c>
       <c r="E178" t="n">
-        <v>2419.52</v>
+        <v>1942.35</v>
       </c>
       <c r="F178" t="n">
-        <v>87.90000000000001</v>
+        <v>400.68</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
@@ -5594,24 +5594,24 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1991.34</v>
+        <v>1441.97</v>
       </c>
       <c r="D179" t="n">
-        <v>2250.21</v>
+        <v>1629.43</v>
       </c>
       <c r="E179" t="n">
-        <v>1991.34</v>
+        <v>1441.97</v>
       </c>
       <c r="F179" t="n">
         <v>0</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
@@ -5623,24 +5623,24 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>2990.06</v>
+        <v>2893.01</v>
       </c>
       <c r="D180" t="n">
-        <v>3378.77</v>
+        <v>3269.1</v>
       </c>
       <c r="E180" t="n">
-        <v>2990.06</v>
+        <v>2893.01</v>
       </c>
       <c r="F180" t="n">
         <v>0</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
@@ -5656,20 +5656,20 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>4832.76</v>
+        <v>3528.03</v>
       </c>
       <c r="D181" t="n">
-        <v>5461.02</v>
+        <v>3986.67</v>
       </c>
       <c r="E181" t="n">
-        <v>4832.76</v>
+        <v>2840.21</v>
       </c>
       <c r="F181" t="n">
-        <v>0</v>
+        <v>687.8200000000001</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -5681,17 +5681,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>824.1799999999999</v>
+        <v>1246.41</v>
       </c>
       <c r="D182" t="n">
-        <v>931.3200000000001</v>
+        <v>1408.44</v>
       </c>
       <c r="E182" t="n">
-        <v>824.1799999999999</v>
+        <v>1246.41</v>
       </c>
       <c r="F182" t="n">
         <v>0</v>
@@ -5710,24 +5710,24 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1961.98</v>
+        <v>1557.95</v>
       </c>
       <c r="D183" t="n">
-        <v>2217.04</v>
+        <v>1760.48</v>
       </c>
       <c r="E183" t="n">
-        <v>1961.98</v>
+        <v>1557.95</v>
       </c>
       <c r="F183" t="n">
         <v>0</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
@@ -5739,24 +5739,24 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>4220.43</v>
+        <v>2409.92</v>
       </c>
       <c r="D184" t="n">
-        <v>4769.09</v>
+        <v>2723.21</v>
       </c>
       <c r="E184" t="n">
-        <v>4220.43</v>
+        <v>2409.92</v>
       </c>
       <c r="F184" t="n">
         <v>0</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -5772,20 +5772,20 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>3074.43</v>
+        <v>3243.13</v>
       </c>
       <c r="D185" t="n">
-        <v>3474.11</v>
+        <v>3664.74</v>
       </c>
       <c r="E185" t="n">
-        <v>3074.43</v>
+        <v>3243.13</v>
       </c>
       <c r="F185" t="n">
         <v>0</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -5801,20 +5801,20 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>3658.56</v>
+        <v>2316.48</v>
       </c>
       <c r="D186" t="n">
-        <v>4134.17</v>
+        <v>2617.62</v>
       </c>
       <c r="E186" t="n">
-        <v>3658.56</v>
+        <v>1923.93</v>
       </c>
       <c r="F186" t="n">
-        <v>0</v>
+        <v>392.55</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
@@ -5830,20 +5830,20 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>4099.34</v>
+        <v>2846.6</v>
       </c>
       <c r="D187" t="n">
-        <v>4632.25</v>
+        <v>3216.66</v>
       </c>
       <c r="E187" t="n">
-        <v>4099.34</v>
+        <v>2846.6</v>
       </c>
       <c r="F187" t="n">
         <v>0</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -5855,24 +5855,24 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1472.31</v>
+        <v>2061.53</v>
       </c>
       <c r="D188" t="n">
-        <v>1663.71</v>
+        <v>2329.53</v>
       </c>
       <c r="E188" t="n">
-        <v>1472.31</v>
+        <v>2061.53</v>
       </c>
       <c r="F188" t="n">
         <v>0</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
@@ -5884,24 +5884,24 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>4434.68</v>
+        <v>2560.65</v>
       </c>
       <c r="D189" t="n">
-        <v>5011.19</v>
+        <v>2893.53</v>
       </c>
       <c r="E189" t="n">
-        <v>4042.08</v>
+        <v>2493.6</v>
       </c>
       <c r="F189" t="n">
-        <v>392.6</v>
+        <v>67.05</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
@@ -5913,24 +5913,24 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>3859.73</v>
+        <v>2420.89</v>
       </c>
       <c r="D190" t="n">
-        <v>4361.49</v>
+        <v>2735.61</v>
       </c>
       <c r="E190" t="n">
-        <v>3859.73</v>
+        <v>2369.48</v>
       </c>
       <c r="F190" t="n">
-        <v>0</v>
+        <v>51.41</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5946,20 +5946,20 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>170.83</v>
+        <v>1732.71</v>
       </c>
       <c r="D191" t="n">
-        <v>193.04</v>
+        <v>1957.96</v>
       </c>
       <c r="E191" t="n">
-        <v>170.83</v>
+        <v>1732.71</v>
       </c>
       <c r="F191" t="n">
         <v>0</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -5975,20 +5975,20 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>664.28</v>
+        <v>2486.34</v>
       </c>
       <c r="D192" t="n">
-        <v>750.64</v>
+        <v>2809.56</v>
       </c>
       <c r="E192" t="n">
-        <v>664.28</v>
+        <v>2486.34</v>
       </c>
       <c r="F192" t="n">
         <v>0</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -6000,24 +6000,24 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>4195.81</v>
+        <v>1723.14</v>
       </c>
       <c r="D193" t="n">
-        <v>4741.27</v>
+        <v>1947.15</v>
       </c>
       <c r="E193" t="n">
-        <v>4195.81</v>
+        <v>1723.14</v>
       </c>
       <c r="F193" t="n">
         <v>0</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
@@ -6029,24 +6029,24 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1536.55</v>
+        <v>1512.2</v>
       </c>
       <c r="D194" t="n">
-        <v>1736.3</v>
+        <v>1708.79</v>
       </c>
       <c r="E194" t="n">
-        <v>1536.55</v>
+        <v>1512.2</v>
       </c>
       <c r="F194" t="n">
         <v>0</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-28</t>
         </is>
       </c>
     </row>
@@ -6058,24 +6058,24 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1037.6</v>
+        <v>4021.7</v>
       </c>
       <c r="D195" t="n">
-        <v>1172.49</v>
+        <v>4544.52</v>
       </c>
       <c r="E195" t="n">
-        <v>1037.47</v>
+        <v>4021.7</v>
       </c>
       <c r="F195" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
@@ -6091,20 +6091,20 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>420.25</v>
+        <v>1071.12</v>
       </c>
       <c r="D196" t="n">
-        <v>474.88</v>
+        <v>1210.37</v>
       </c>
       <c r="E196" t="n">
-        <v>420.25</v>
+        <v>1071.12</v>
       </c>
       <c r="F196" t="n">
         <v>0</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -6116,24 +6116,24 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>585.62</v>
+        <v>1814.15</v>
       </c>
       <c r="D197" t="n">
-        <v>661.75</v>
+        <v>2049.99</v>
       </c>
       <c r="E197" t="n">
-        <v>585.62</v>
+        <v>1814.15</v>
       </c>
       <c r="F197" t="n">
         <v>0</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -6145,24 +6145,24 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>3437.94</v>
+        <v>2119.55</v>
       </c>
       <c r="D198" t="n">
-        <v>3884.87</v>
+        <v>2395.09</v>
       </c>
       <c r="E198" t="n">
-        <v>3437.94</v>
+        <v>2119.55</v>
       </c>
       <c r="F198" t="n">
         <v>0</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
@@ -6178,20 +6178,20 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>1102.98</v>
+        <v>756.6</v>
       </c>
       <c r="D199" t="n">
-        <v>1246.37</v>
+        <v>854.96</v>
       </c>
       <c r="E199" t="n">
-        <v>1102.98</v>
+        <v>756.6</v>
       </c>
       <c r="F199" t="n">
         <v>0</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -6203,24 +6203,24 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>2251.45</v>
+        <v>905.66</v>
       </c>
       <c r="D200" t="n">
-        <v>2544.14</v>
+        <v>1023.4</v>
       </c>
       <c r="E200" t="n">
-        <v>2251.45</v>
+        <v>905.66</v>
       </c>
       <c r="F200" t="n">
         <v>0</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
@@ -6232,20 +6232,20 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>1656.41</v>
+        <v>4749.51</v>
       </c>
       <c r="D201" t="n">
-        <v>1871.74</v>
+        <v>5366.95</v>
       </c>
       <c r="E201" t="n">
-        <v>1372.18</v>
+        <v>4018.64</v>
       </c>
       <c r="F201" t="n">
-        <v>284.23</v>
+        <v>730.87</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
